--- a/prix/hammerite.xlsx
+++ b/prix/hammerite.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\peintures\prix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{495DBCDB-69ED-4073-BE15-CAE90A926FFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A810815-E276-4069-9FF7-3A527F397239}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="19416" windowHeight="11016" xr2:uid="{6E95DC93-531D-460D-9A06-44397A8920D7}"/>
   </bookViews>
@@ -1344,7 +1344,7 @@
         <v>7</v>
       </c>
       <c r="F3" s="11">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -1364,7 +1364,7 @@
         <v>8</v>
       </c>
       <c r="F4" s="11">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -1544,7 +1544,7 @@
         <v>17</v>
       </c>
       <c r="F13" s="11">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
@@ -1584,7 +1584,7 @@
         <v>19</v>
       </c>
       <c r="F15" s="11">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
@@ -1764,7 +1764,7 @@
         <v>28</v>
       </c>
       <c r="F24" s="11">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
@@ -1904,7 +1904,7 @@
         <v>35</v>
       </c>
       <c r="F31" s="11">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
@@ -2004,7 +2004,7 @@
         <v>40</v>
       </c>
       <c r="F36" s="11">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
@@ -2304,7 +2304,7 @@
         <v>55</v>
       </c>
       <c r="F51" s="11">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
@@ -2504,7 +2504,7 @@
         <v>65</v>
       </c>
       <c r="F61" s="11">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
@@ -2644,7 +2644,7 @@
         <v>72</v>
       </c>
       <c r="F68" s="11">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
@@ -2784,7 +2784,7 @@
         <v>79</v>
       </c>
       <c r="F75" s="11">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
